--- a/September-2026.xlsx
+++ b/September-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD524603-6017-4A98-A515-BC588C7A9FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB8B738-F043-4148-8F19-12A96A1B743C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -572,16 +572,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="C2" s="4">
-        <v>349</v>
+        <v>518</v>
       </c>
       <c r="D2" s="9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" s="13">
-        <v>2.5</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -591,16 +591,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="C3" s="4">
-        <v>408</v>
+        <v>627</v>
       </c>
       <c r="D3" s="9">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E3" s="13">
-        <v>2.1666666666666665</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -610,16 +610,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>144</v>
+        <v>303</v>
       </c>
       <c r="C4" s="4">
-        <v>380</v>
+        <v>602</v>
       </c>
       <c r="D4" s="9">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E4" s="13">
-        <v>1.1666666666666667</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -629,13 +629,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="C5" s="4">
-        <v>327</v>
+        <v>502</v>
       </c>
       <c r="D5" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E5" s="13">
         <v>2</v>
@@ -648,16 +648,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>183</v>
+        <v>255</v>
       </c>
       <c r="C6" s="4">
-        <v>335</v>
+        <v>477</v>
       </c>
       <c r="D6" s="9">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E6" s="13">
-        <v>3.6666666666666665</v>
+        <v>3.5555555555555554</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -667,13 +667,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>227</v>
+        <v>365</v>
       </c>
       <c r="C7" s="4">
-        <v>335</v>
+        <v>523</v>
       </c>
       <c r="D7" s="9">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E7" s="13">
         <v>3.6666666666666665</v>
@@ -692,10 +692,10 @@
         <v>480</v>
       </c>
       <c r="D8" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="13">
-        <v>2.3333333333333335</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -705,16 +705,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="C9" s="4">
-        <v>467</v>
+        <v>705</v>
       </c>
       <c r="D9" s="9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" s="13">
-        <v>2.8333333333333335</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -724,16 +724,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="C10" s="4">
-        <v>274</v>
+        <v>464</v>
       </c>
       <c r="D10" s="9">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E10" s="13">
-        <v>1</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -743,16 +743,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="C11" s="4">
-        <v>454</v>
+        <v>605</v>
       </c>
       <c r="D11" s="9">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E11" s="13">
-        <v>3.5</v>
+        <v>2.8888888888888888</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -762,13 +762,13 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="C12" s="4">
-        <v>263</v>
+        <v>399</v>
       </c>
       <c r="D12" s="9">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E12" s="13">
         <v>2.6666666666666665</v>
@@ -781,16 +781,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>170</v>
+        <v>256</v>
       </c>
       <c r="C13" s="4">
-        <v>330</v>
+        <v>530</v>
       </c>
       <c r="D13" s="9">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E13" s="13">
-        <v>2.8333333333333335</v>
+        <v>2.8888888888888888</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -800,16 +800,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="C14" s="4">
-        <v>287</v>
+        <v>491</v>
       </c>
       <c r="D14" s="9">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E14" s="13">
-        <v>1.6666666666666667</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -819,16 +819,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="C15" s="4">
-        <v>437</v>
+        <v>653</v>
       </c>
       <c r="D15" s="9">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" s="13">
-        <v>2</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -838,16 +838,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>191</v>
+        <v>273</v>
       </c>
       <c r="C16" s="4">
-        <v>288</v>
+        <v>433</v>
       </c>
       <c r="D16" s="9">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E16" s="13">
-        <v>3.6666666666666665</v>
+        <v>3.1111111111111112</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -857,16 +857,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>150</v>
+        <v>243</v>
       </c>
       <c r="C17" s="4">
-        <v>457</v>
+        <v>693</v>
       </c>
       <c r="D17" s="9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17" s="13">
-        <v>2</v>
+        <v>1.5555555555555556</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -876,16 +876,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4">
-        <v>330</v>
+        <v>403</v>
       </c>
       <c r="D18" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="13">
-        <v>0.66666666666666663</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -895,16 +895,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="C19" s="4">
-        <v>390</v>
+        <v>588</v>
       </c>
       <c r="D19" s="9">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E19" s="13">
-        <v>3</v>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -912,16 +912,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>2826</v>
+        <v>4472</v>
       </c>
       <c r="C20" s="6">
-        <v>6591</v>
+        <v>9693</v>
       </c>
       <c r="D20" s="10">
-        <v>260</v>
+        <v>393</v>
       </c>
       <c r="E20" s="14">
-        <v>2.4074074074074074</v>
+        <v>2.4259259259259256</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1001,10 +1001,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="31" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="31" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1131,9 +1131,15 @@
       <c r="H2" s="4">
         <v>101</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
+      <c r="I2" s="4">
+        <v>100</v>
+      </c>
+      <c r="J2" s="4">
+        <v>102</v>
+      </c>
+      <c r="K2" s="4">
+        <v>97</v>
+      </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -1155,7 +1161,7 @@
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="9">
-        <v>604</v>
+        <v>903</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1183,9 +1189,15 @@
       <c r="H3" s="4">
         <v>103</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
+      <c r="I3" s="4">
+        <v>108</v>
+      </c>
+      <c r="J3" s="4">
+        <v>99</v>
+      </c>
+      <c r="K3" s="4">
+        <v>107</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -1207,7 +1219,7 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="9">
-        <v>546</v>
+        <v>860</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -1235,9 +1247,15 @@
       <c r="H4" s="4">
         <v>110</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="I4" s="4">
+        <v>143</v>
+      </c>
+      <c r="J4" s="4">
+        <v>109</v>
+      </c>
+      <c r="K4" s="4">
+        <v>129</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -1259,7 +1277,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="9">
-        <v>524</v>
+        <v>905</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1287,9 +1305,15 @@
       <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="I5" s="4">
+        <v>106</v>
+      </c>
+      <c r="J5" s="4">
+        <v>102</v>
+      </c>
+      <c r="K5" s="4">
+        <v>92</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
@@ -1311,7 +1335,7 @@
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="9">
-        <v>456</v>
+        <v>756</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1339,9 +1363,15 @@
       <c r="H6" s="4">
         <v>120</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
@@ -1391,9 +1421,15 @@
       <c r="H7" s="4">
         <v>107</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="I7" s="4">
+        <v>114</v>
+      </c>
+      <c r="J7" s="4">
+        <v>104</v>
+      </c>
+      <c r="K7" s="4">
+        <v>108</v>
+      </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
@@ -1415,7 +1451,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="9">
-        <v>642</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1443,9 +1479,15 @@
       <c r="H8" s="4">
         <v>112</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
+      <c r="I8" s="4">
+        <v>97</v>
+      </c>
+      <c r="J8" s="4">
+        <v>83</v>
+      </c>
+      <c r="K8" s="4">
+        <v>113</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
@@ -1467,7 +1509,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="9">
-        <v>387</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1495,9 +1537,15 @@
       <c r="H9" s="4">
         <v>106</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>105</v>
+      </c>
+      <c r="K9" s="4">
+        <v>116</v>
+      </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -1519,7 +1567,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="9">
-        <v>621</v>
+        <v>842</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1547,9 +1595,15 @@
       <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
+      <c r="I10" s="4">
+        <v>111</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <v>110</v>
+      </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -1571,7 +1625,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="9">
-        <v>375</v>
+        <v>596</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1599,9 +1653,15 @@
       <c r="H11" s="4">
         <v>106</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="I11" s="4">
+        <v>97</v>
+      </c>
+      <c r="J11" s="4">
+        <v>74</v>
+      </c>
+      <c r="K11" s="4">
+        <v>115</v>
+      </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
@@ -1623,7 +1683,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="9">
-        <v>500</v>
+        <v>786</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1651,9 +1711,15 @@
       <c r="H12" s="4">
         <v>98</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="I12" s="4">
+        <v>98</v>
+      </c>
+      <c r="J12" s="4">
+        <v>88</v>
+      </c>
+      <c r="K12" s="4">
+        <v>107</v>
+      </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -1675,7 +1741,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="9">
-        <v>424</v>
+        <v>717</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1703,9 +1769,15 @@
       <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="I13" s="4">
+        <v>102</v>
+      </c>
+      <c r="J13" s="4">
+        <v>103</v>
+      </c>
+      <c r="K13" s="4">
+        <v>94</v>
+      </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -1727,7 +1799,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="9">
-        <v>550</v>
+        <v>849</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1755,9 +1827,15 @@
       <c r="H14" s="4">
         <v>104</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
+      <c r="I14" s="4">
+        <v>115</v>
+      </c>
+      <c r="J14" s="4">
+        <v>107</v>
+      </c>
+      <c r="K14" s="4">
+        <v>107</v>
+      </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -1779,7 +1857,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="9">
-        <v>607</v>
+        <v>936</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -1807,9 +1885,15 @@
       <c r="H15" s="4">
         <v>102</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>103</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -1831,7 +1915,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="9">
-        <v>444</v>
+        <v>547</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -1859,9 +1943,15 @@
       <c r="H16" s="4">
         <v>98</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="I16" s="4">
+        <v>107</v>
+      </c>
+      <c r="J16" s="4">
+        <v>105</v>
+      </c>
+      <c r="K16" s="4">
+        <v>104</v>
+      </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -1883,7 +1973,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="9">
-        <v>532</v>
+        <v>848</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -1911,9 +2001,15 @@
       <c r="H17" s="4">
         <v>126</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="I17" s="4">
+        <v>109</v>
+      </c>
+      <c r="J17" s="4">
+        <v>118</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -1935,7 +2031,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="9">
-        <v>479</v>
+        <v>706</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -1963,9 +2059,15 @@
       <c r="H18" s="4">
         <v>124</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="I18" s="4">
+        <v>115</v>
+      </c>
+      <c r="J18" s="4">
+        <v>94</v>
+      </c>
+      <c r="K18" s="4">
+        <v>117</v>
+      </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -1987,7 +2089,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="9">
-        <v>562</v>
+        <v>888</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -2015,9 +2117,15 @@
       <c r="H19" s="4">
         <v>109</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>108</v>
+      </c>
+      <c r="K19" s="4">
+        <v>106</v>
+      </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
@@ -2039,7 +2147,7 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="9">
-        <v>518</v>
+        <v>732</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -2067,9 +2175,15 @@
       <c r="H20" s="6">
         <v>1626</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
+      <c r="I20" s="6">
+        <v>1522</v>
+      </c>
+      <c r="J20" s="6">
+        <v>1604</v>
+      </c>
+      <c r="K20" s="6">
+        <v>1622</v>
+      </c>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
@@ -2091,7 +2205,7 @@
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
       <c r="AF20" s="10">
-        <v>9417</v>
+        <v>14165</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
@@ -2158,7 +2272,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.4074074074074074</v>
+        <v>2.4259259259259256</v>
       </c>
     </row>
   </sheetData>
